--- a/outputs/Assignment_02_Predictions.xlsx
+++ b/outputs/Assignment_02_Predictions.xlsx
@@ -517,31 +517,31 @@
         <v>74</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>82.62</v>
+        <v>83.26000000000001</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>82.79000000000001</v>
+        <v>83.23</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>84.56999999999999</v>
+        <v>83.63</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>74.34</v>
+        <v>72.56</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>74</v>
+        <v>74.42</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>75.69</v>
+        <v>71.69</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>72.04000000000001</v>
+        <v>73.48999999999999</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>72.83</v>
+        <v>74.48</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>73.28</v>
+        <v>73.08</v>
       </c>
     </row>
     <row r="3">
@@ -554,13 +554,13 @@
         <v>0</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>39.04</v>
+        <v>45.3</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>45.86</v>
+        <v>42.04</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>24.42</v>
+        <v>0</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>0</v>
@@ -569,16 +569,16 @@
         <v>0</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>24.92</v>
+        <v>0</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>24.78</v>
+        <v>0</v>
       </c>
       <c r="J3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>24.92</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -591,13 +591,13 @@
         <v>0</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>39.04</v>
+        <v>45.3</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>45.86</v>
+        <v>42.04</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>24.42</v>
+        <v>0</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>0</v>
@@ -606,16 +606,16 @@
         <v>0</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>24.92</v>
+        <v>0</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>24.78</v>
+        <v>0</v>
       </c>
       <c r="J4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>24.92</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -628,31 +628,31 @@
         <v>60</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>64.47</v>
+        <v>62.18</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>63.95</v>
+        <v>59.98</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>61.97</v>
+        <v>60.1</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>61.49</v>
+        <v>58.61</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>60.11</v>
+        <v>57.61</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>57.82</v>
+        <v>56.85</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>58.53</v>
+        <v>56.63</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>62.07</v>
+        <v>58.23</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>60.74</v>
+        <v>57.88</v>
       </c>
     </row>
     <row r="6">
@@ -665,31 +665,31 @@
         <v>77</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>76.47</v>
+        <v>77.34</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>77.13</v>
+        <v>78.48</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>76.56</v>
+        <v>73.88</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>81.54000000000001</v>
+        <v>79.65000000000001</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>81.36</v>
+        <v>79.94</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>77.45</v>
+        <v>79.58</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>80.67</v>
+        <v>80.75</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>85.23</v>
+        <v>79.56999999999999</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>77.51000000000001</v>
+        <v>76.43000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -702,31 +702,31 @@
         <v>70</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>71.84</v>
+        <v>69.16</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>68.98999999999999</v>
+        <v>69.51000000000001</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>72.23</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>66.69</v>
+        <v>67.08</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>65.47</v>
+        <v>66.64</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>70.59</v>
+        <v>69.05</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>66.37</v>
+        <v>67.42</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>67.15000000000001</v>
+        <v>68.22</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>64.73</v>
+        <v>65.95999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -739,31 +739,31 @@
         <v>70</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>80.7</v>
+        <v>77.12</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>76.31999999999999</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>77.41</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>74.52</v>
+        <v>70.11</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>75.7</v>
+        <v>72.33</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>71.64</v>
+        <v>71.47</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>68.93000000000001</v>
+        <v>70.29000000000001</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>76.48999999999999</v>
+        <v>70.45999999999999</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>65.66</v>
+        <v>67.20999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -776,31 +776,31 @@
         <v>54</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>46.04</v>
+        <v>47.76</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>48.08</v>
+        <v>48.61</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>51.44</v>
+        <v>50.26</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>51.36</v>
+        <v>51.87</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>46.04</v>
+        <v>48.18</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>51.73</v>
+        <v>49.49</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>51.53</v>
+        <v>47.86</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>48.64</v>
+        <v>47.87</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>52.8</v>
+        <v>47.94</v>
       </c>
     </row>
     <row r="10">
@@ -813,31 +813,31 @@
         <v>64</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>72.45</v>
+        <v>73.29000000000001</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>72.45999999999999</v>
+        <v>74.04000000000001</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>70.67</v>
+        <v>73.33</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>66.81</v>
+        <v>67.52</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>62.32</v>
+        <v>66.76000000000001</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>68.92</v>
+        <v>69.52</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>67.13</v>
+        <v>68.45</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>66.23</v>
+        <v>68.75</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>64.78</v>
+        <v>67.33</v>
       </c>
     </row>
     <row r="11">
@@ -850,31 +850,31 @@
         <v>63</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>72.40000000000001</v>
+        <v>70.69</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>70.73</v>
+        <v>71.70999999999999</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>69.51000000000001</v>
+        <v>71.69</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>65.03</v>
+        <v>65.23999999999999</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>65.44</v>
+        <v>66.23999999999999</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>65.28</v>
+        <v>66.5</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>65.31</v>
+        <v>67.20999999999999</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>63.97</v>
+        <v>66.27</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>64.66</v>
+        <v>65.69</v>
       </c>
     </row>
     <row r="12">
@@ -887,31 +887,31 @@
         <v>61</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>63.24</v>
+        <v>70.14</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>70.88</v>
+        <v>70.64</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>67.40000000000001</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>58.16</v>
+        <v>60.21</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>61.35</v>
+        <v>61.33</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>59.09</v>
+        <v>62.63</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>57.98</v>
+        <v>62.67</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>68.83</v>
+        <v>62.36</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>56.67</v>
+        <v>59.22</v>
       </c>
     </row>
     <row r="13">
@@ -924,31 +924,31 @@
         <v>58</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>59.26</v>
+        <v>58.87</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>58.99</v>
+        <v>58.75</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>59.68</v>
+        <v>59.75</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>57.77</v>
+        <v>58.19</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>57.32</v>
+        <v>58.09</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>58.26</v>
+        <v>56.25</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>56.72</v>
+        <v>55.88</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>53.03</v>
+        <v>57.58</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>57.66</v>
+        <v>56.75</v>
       </c>
     </row>
     <row r="14">
@@ -961,31 +961,31 @@
         <v>63</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>41.85</v>
+        <v>45.3</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>45.86</v>
+        <v>42.04</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>31.4</v>
+        <v>43.78</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>46.64</v>
+        <v>51.53</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>58.55</v>
+        <v>51.22</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>36.95</v>
+        <v>55.18</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>47.45</v>
+        <v>55.16</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>65.98999999999999</v>
+        <v>52.69</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>37.01</v>
+        <v>52.47</v>
       </c>
     </row>
     <row r="15">
@@ -998,31 +998,31 @@
         <v>71</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>76.13</v>
+        <v>73.48999999999999</v>
       </c>
       <c r="D15" s="3" t="n">
+        <v>74.19</v>
+      </c>
+      <c r="E15" s="3" t="n">
         <v>73.5</v>
       </c>
-      <c r="E15" s="3" t="n">
-        <v>74.63</v>
-      </c>
       <c r="F15" s="3" t="n">
-        <v>62.61</v>
+        <v>64.02</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>62.42</v>
+        <v>64.45</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>59.35</v>
+        <v>64.48</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>63.14</v>
+        <v>65.77</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>66.01000000000001</v>
+        <v>67.3</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>66.34</v>
+        <v>67.18000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -1035,31 +1035,31 @@
         <v>65</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>56.23</v>
+        <v>59.93</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>59.7</v>
+        <v>58.73</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>56.8</v>
+        <v>57.23</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>61.38</v>
+        <v>60.89</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>60.48</v>
+        <v>60.83</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>64.84999999999999</v>
+        <v>60.99</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>61.66</v>
+        <v>60.31</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>63.43</v>
+        <v>60.43</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>62.07</v>
+        <v>59.97</v>
       </c>
     </row>
     <row r="17">
@@ -1072,31 +1072,31 @@
         <v>32</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>41.08</v>
+        <v>48.24</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>48.07</v>
+        <v>49.2</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>45.23</v>
+        <v>48.35</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>40.99</v>
+        <v>45.65</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>40.1</v>
+        <v>42.27</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>47.56</v>
+        <v>43.68</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>47.1</v>
+        <v>43.79</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>44.37</v>
+        <v>41.44</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>47.46</v>
+        <v>40.3</v>
       </c>
     </row>
     <row r="18">
@@ -1109,31 +1109,31 @@
         <v>78</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>80.53</v>
+        <v>77.06</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>76.2</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>78.3</v>
+        <v>75.44</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>71.73999999999999</v>
+        <v>67.2</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>70.39</v>
+        <v>67.11</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>69.28</v>
+        <v>70.25</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>69.33</v>
+        <v>71.48</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>77.04000000000001</v>
+        <v>72.86</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>75.98999999999999</v>
+        <v>75.45999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -1146,31 +1146,31 @@
         <v>42</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>41.85</v>
+        <v>45.3</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>45.86</v>
+        <v>42.04</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>27.72</v>
+        <v>42.43</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>36.36</v>
+        <v>45.07</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>39.33</v>
+        <v>43.63</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>30.8</v>
+        <v>43.08</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>32.35</v>
+        <v>42.45</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>35.48</v>
+        <v>41.27</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>32.05</v>
+        <v>40.14</v>
       </c>
     </row>
     <row r="20">
@@ -1183,31 +1183,31 @@
         <v>50</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>60.64</v>
+        <v>61.62</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>59.43</v>
+        <v>56.33</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>64.03</v>
+        <v>56.72</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>57.1</v>
+        <v>52.75</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>54.92</v>
+        <v>49.13</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>56.72</v>
+        <v>49.81</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>55.05</v>
+        <v>48.7</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>56.1</v>
+        <v>47.52</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>56.33</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="21">
@@ -1220,31 +1220,31 @@
         <v>55</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>53.28</v>
+        <v>55.99</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>54.4</v>
+        <v>55.69</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>55.57</v>
+        <v>56.41</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>54.07</v>
+        <v>53.59</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>56.87</v>
+        <v>54.2</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>55.19</v>
+        <v>55.32</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>53.83</v>
+        <v>54.41</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>55.72</v>
+        <v>53.84</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>53.72</v>
+        <v>52.66</v>
       </c>
     </row>
     <row r="22">
@@ -1257,31 +1257,31 @@
         <v>67</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>61.85</v>
+        <v>66.44</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>64.31</v>
+        <v>66.06999999999999</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>66</v>
+        <v>68.91</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>69.97</v>
+        <v>69.64</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>71.86</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>71.68000000000001</v>
+        <v>70.77</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>70.5</v>
+        <v>70.42</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>75.52</v>
+        <v>70.14</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>68.81999999999999</v>
+        <v>70.53</v>
       </c>
     </row>
     <row r="23">
@@ -1294,28 +1294,28 @@
         <v>58</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>74.66</v>
+        <v>68.89</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>66.42</v>
+        <v>63.23</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>48.76</v>
+        <v>63.15</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>41.91</v>
+        <v>54.27</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>53.35</v>
+        <v>55.05</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>56.83</v>
+        <v>55.29</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>58.3</v>
+        <v>56.99</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>60.82</v>
+        <v>57.77</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>57.3</v>
@@ -1331,31 +1331,31 @@
         <v>49</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>41.85</v>
+        <v>45.3</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>45.86</v>
+        <v>42.04</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>26.14</v>
+        <v>42.32</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>26.17</v>
+        <v>38.65</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>34.15</v>
+        <v>36.16</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>24.87</v>
+        <v>41.27</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>24.99</v>
+        <v>41.78</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>49.47</v>
+        <v>41.61</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>26.58</v>
+        <v>44.58</v>
       </c>
     </row>
     <row r="25">
@@ -1368,31 +1368,31 @@
         <v>74</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>76.45999999999999</v>
+        <v>77.28</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>76.95</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>78.81999999999999</v>
+        <v>80.48</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>73.03</v>
+        <v>71.04000000000001</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>75.70999999999999</v>
+        <v>71.16</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>78.31</v>
+        <v>74.03</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>77.2</v>
+        <v>77.20999999999999</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>77.98999999999999</v>
+        <v>75.55</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>71.28</v>
+        <v>73.51000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -1405,31 +1405,31 @@
         <v>72</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>65.31999999999999</v>
+        <v>67.14</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>66.45999999999999</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>69.20999999999999</v>
+        <v>70.13</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>63.95</v>
+        <v>65.05</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>65.90000000000001</v>
+        <v>64.69</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>68.06</v>
+        <v>69.23</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>69.14</v>
+        <v>69.01000000000001</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>72.56</v>
+        <v>70.56</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>69.75</v>
+        <v>71.64</v>
       </c>
     </row>
     <row r="27">
@@ -1442,31 +1442,31 @@
         <v>34</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>42.85</v>
+        <v>46.16</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>47.39</v>
+        <v>48.31</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>47.77</v>
+        <v>47.5</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>34.79</v>
+        <v>38.19</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>31.28</v>
+        <v>37.07</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>48.26</v>
+        <v>41.39</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>46.99</v>
+        <v>39.88</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>37.77</v>
+        <v>38.2</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>47.46</v>
+        <v>37.4</v>
       </c>
     </row>
     <row r="28">
@@ -1479,31 +1479,31 @@
         <v>53</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>43.45</v>
+        <v>49.39</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>49.87</v>
+        <v>51.72</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>49.97</v>
+        <v>51.27</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>53.83</v>
+        <v>55.6</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>56.65</v>
+        <v>56.38</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>52.76</v>
+        <v>56.7</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>55.33</v>
+        <v>58.28</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>61.68</v>
+        <v>56.97</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>52.85</v>
+        <v>55.07</v>
       </c>
     </row>
     <row r="29">
@@ -1516,31 +1516,31 @@
         <v>31</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>41.85</v>
+        <v>45.3</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>45.86</v>
+        <v>42.04</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>27.72</v>
+        <v>42.43</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>27.63</v>
+        <v>39.64</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>30.3</v>
+        <v>38.15</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>29.4</v>
+        <v>37.4</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>29.76</v>
+        <v>39.37</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>31.96</v>
+        <v>37.97</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>29.8</v>
+        <v>36.94</v>
       </c>
     </row>
     <row r="30">
@@ -1553,31 +1553,31 @@
         <v>54</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>41.85</v>
+        <v>45.3</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>45.86</v>
+        <v>42.04</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>30.88</v>
+        <v>43.33</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>36.11</v>
+        <v>44.89</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>44.09</v>
+        <v>43.65</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>33.21</v>
+        <v>47.46</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>30.26</v>
+        <v>47.45</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>53.71</v>
+        <v>45.07</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>31.04</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="31">
@@ -1590,31 +1590,31 @@
         <v>60</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>65.59</v>
+        <v>61.86</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>61.97</v>
+        <v>62.19</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>67.48</v>
+        <v>63.56</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>61.1</v>
+        <v>58.75</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>60.6</v>
+        <v>58.59</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>62.45</v>
+        <v>59.5</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>60.94</v>
+        <v>60.05</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>62.29</v>
+        <v>60.26</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>59.22</v>
+        <v>59.1</v>
       </c>
     </row>
     <row r="32">
@@ -1627,31 +1627,31 @@
         <v>57</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>42.09</v>
+        <v>48.5</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>48.55</v>
+        <v>50.83</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>48.15</v>
+        <v>50.52</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>49.23</v>
+        <v>51.86</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>49.86</v>
+        <v>52.11</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>51.9</v>
+        <v>52.15</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>51.97</v>
+        <v>54.03</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>56.14</v>
+        <v>52.48</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>52.34</v>
+        <v>50.97</v>
       </c>
     </row>
     <row r="33">
@@ -1664,31 +1664,31 @@
         <v>54</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>55.35</v>
+        <v>62.13</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>64.31999999999999</v>
+        <v>58.73</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>41.12</v>
+        <v>58.4</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>41.05</v>
+        <v>54.4</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>43.32</v>
+        <v>54.82</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>45.68</v>
+        <v>57.69</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>44</v>
+        <v>57.1</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>54.15</v>
+        <v>57.59</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>42.21</v>
+        <v>54.66</v>
       </c>
     </row>
     <row r="34">
@@ -1701,31 +1701,31 @@
         <v>47</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>50.13</v>
+        <v>48.89</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>48.31</v>
+        <v>45.58</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>44.93</v>
+        <v>46.45</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>50.82</v>
+        <v>47.69</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>49.13</v>
+        <v>43.47</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>53.46</v>
+        <v>45.11</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>53.46</v>
+        <v>43.16</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>57.99</v>
+        <v>45.41</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>54.1</v>
+        <v>46.44</v>
       </c>
     </row>
     <row r="35">
@@ -1738,31 +1738,31 @@
         <v>67</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>72.2</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>66.87</v>
+        <v>64.95</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>66.61</v>
+        <v>63.8</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>66.14</v>
+        <v>63.87</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>68.5</v>
+        <v>63.86</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>59.38</v>
+        <v>63.96</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>64.02</v>
+        <v>65.11</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>75.06999999999999</v>
+        <v>66.09</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>63</v>
+        <v>64.52</v>
       </c>
     </row>
     <row r="36">
@@ -1775,31 +1775,31 @@
         <v>29</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>39.04</v>
+        <v>45.3</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>45.86</v>
+        <v>42.04</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>39.69</v>
+        <v>43.67</v>
       </c>
       <c r="F36" s="3" t="n">
+        <v>37.94</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>36.73</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>36.96</v>
+      </c>
+      <c r="I36" s="3" t="n">
+        <v>38.04</v>
+      </c>
+      <c r="J36" s="3" t="n">
+        <v>36.34</v>
+      </c>
+      <c r="K36" s="3" t="n">
         <v>34.22</v>
-      </c>
-      <c r="G36" s="3" t="n">
-        <v>38.15</v>
-      </c>
-      <c r="H36" s="3" t="n">
-        <v>47.56</v>
-      </c>
-      <c r="I36" s="3" t="n">
-        <v>46.99</v>
-      </c>
-      <c r="J36" s="3" t="n">
-        <v>46.98</v>
-      </c>
-      <c r="K36" s="3" t="n">
-        <v>47.46</v>
       </c>
     </row>
     <row r="37">
@@ -1812,31 +1812,31 @@
         <v>37</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>41.86</v>
+        <v>48.83</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>48.67</v>
+        <v>50.59</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>45.04</v>
+        <v>50.34</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>42.09</v>
+        <v>47.43</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>37</v>
+        <v>43.02</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>47.42</v>
+        <v>45.84</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>47.35</v>
+        <v>45.01</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>47.74</v>
+        <v>45.05</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>47.91</v>
+        <v>44.54</v>
       </c>
     </row>
     <row r="38">
@@ -1849,31 +1849,31 @@
         <v>71</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>60.82</v>
+        <v>59.09</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>58.56</v>
+        <v>59.49</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>64.04000000000001</v>
+        <v>62.66</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>64.76000000000001</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>65.37</v>
+        <v>65.20999999999999</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>66.01000000000001</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>66.09</v>
+        <v>65.95</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>68.86</v>
+        <v>68.25</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>69.59999999999999</v>
+        <v>69.78</v>
       </c>
     </row>
     <row r="39">
@@ -1886,31 +1886,31 @@
         <v>62</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>70.69</v>
+        <v>70.09</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>70.34</v>
+        <v>70.44</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>74.3</v>
+        <v>76.83</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>69.48</v>
+        <v>70.65000000000001</v>
       </c>
       <c r="G39" s="3" t="n">
+        <v>70.56</v>
+      </c>
+      <c r="H39" s="3" t="n">
         <v>70.09</v>
       </c>
-      <c r="H39" s="3" t="n">
-        <v>71</v>
-      </c>
       <c r="I39" s="3" t="n">
-        <v>67.92</v>
+        <v>68.7</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>66.02</v>
+        <v>69.45</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>66.68000000000001</v>
+        <v>69.3</v>
       </c>
     </row>
     <row r="40">
@@ -1923,31 +1923,31 @@
         <v>47</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>55.62</v>
+        <v>53.21</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>48.8</v>
+        <v>46.19</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>53.65</v>
+        <v>44.99</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>53.45</v>
+        <v>46.82</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>43.63</v>
+        <v>45.28</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>31.4</v>
+        <v>44.2</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>31.87</v>
+        <v>42.88</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>38.27</v>
+        <v>42.74</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>31.89</v>
+        <v>42.47</v>
       </c>
     </row>
   </sheetData>
@@ -2033,25 +2033,25 @@
         <v>86</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>67.94</v>
+        <v>66.06</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>80.37</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>82.04000000000001</v>
+        <v>80.77</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>80.54000000000001</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>82.17</v>
+        <v>82.22</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>82.09</v>
+        <v>83.51000000000001</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>82.87</v>
+        <v>82.09999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -2064,22 +2064,22 @@
         <v>3</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>42.41</v>
+        <v>2.36</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>2.36</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>40.47</v>
+        <v>2.36</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>37.29</v>
+        <v>2.36</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>37.73</v>
+        <v>2.36</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>36.62</v>
+        <v>2.36</v>
       </c>
       <c r="I3" s="3" t="n">
         <v>2.36</v>
@@ -2095,25 +2095,25 @@
         <v>74</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>46.18</v>
+        <v>53.03</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>67.13</v>
+        <v>72.61</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>70.70999999999999</v>
+        <v>72.75</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>69.23</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>75.93000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>75.22</v>
+        <v>74.65000000000001</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>72.87</v>
+        <v>74.70999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -2126,25 +2126,25 @@
         <v>70</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>57.55</v>
+        <v>60.38</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>64.14</v>
+        <v>66.29000000000001</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>66.05</v>
+        <v>66.41</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>64.54000000000001</v>
+        <v>66.45</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>64.45999999999999</v>
+        <v>66.81</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>63.9</v>
+        <v>66.06999999999999</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>60.53</v>
+        <v>64.91</v>
       </c>
     </row>
     <row r="6">
@@ -2157,25 +2157,25 @@
         <v>66</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>68.59999999999999</v>
+        <v>66.93000000000001</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>67.43000000000001</v>
+        <v>67.78</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>61.53</v>
+        <v>68</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>65.56</v>
+        <v>68.05</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>65.83</v>
+        <v>67.93000000000001</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>69.64</v>
+        <v>68.28</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>63.12</v>
+        <v>64.86</v>
       </c>
     </row>
     <row r="7">
@@ -2188,22 +2188,22 @@
         <v>3</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>42.41</v>
+        <v>2.36</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2.36</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>40.47</v>
+        <v>2.36</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>37.29</v>
+        <v>2.36</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>37.73</v>
+        <v>2.36</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>36.62</v>
+        <v>2.36</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>2.36</v>
@@ -2219,25 +2219,25 @@
         <v>67</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>74.3</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>67.31</v>
+        <v>67.09</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>65.17</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>64.44</v>
+        <v>66.77</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>64.5</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="H8" s="3" t="n">
+        <v>66.25</v>
+      </c>
+      <c r="I8" s="3" t="n">
         <v>64.34999999999999</v>
-      </c>
-      <c r="I8" s="3" t="n">
-        <v>62.7</v>
       </c>
     </row>
     <row r="9">
@@ -2250,25 +2250,25 @@
         <v>65</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>77.73</v>
+        <v>75.12</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>70.26000000000001</v>
+        <v>67.19</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>64.94</v>
+        <v>67.20999999999999</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>67.13</v>
+        <v>67.34</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>66.22</v>
+        <v>67.70999999999999</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>66.08</v>
+        <v>67.47</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>66.47</v>
+        <v>64.56999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -2281,25 +2281,25 @@
         <v>78</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>70.69</v>
+        <v>70.18000000000001</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>78.12</v>
+        <v>77.67</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>74.29000000000001</v>
+        <v>77.16</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>73.08</v>
+        <v>77.19</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>74.14</v>
+        <v>76.54000000000001</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>75.97</v>
+        <v>76.95999999999999</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>72.62</v>
+        <v>72.56999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -2312,25 +2312,25 @@
         <v>65</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>61.39</v>
+        <v>62.18</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>61.37</v>
+        <v>63.45</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>60.71</v>
+        <v>63.39</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>63.19</v>
+        <v>63.36</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>63.3</v>
+        <v>62.42</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>61.75</v>
+        <v>62.23</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>60.62</v>
+        <v>63.21</v>
       </c>
     </row>
     <row r="12">
@@ -2343,25 +2343,25 @@
         <v>52</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>62.8</v>
+        <v>63.77</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>50.41</v>
+        <v>53.24</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>52</v>
+        <v>53.03</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>52.28</v>
+        <v>53.14</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>52.66</v>
+        <v>53.58</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>52.3</v>
+        <v>52.65</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>46.36</v>
+        <v>50.25</v>
       </c>
     </row>
     <row r="13">
@@ -2374,25 +2374,25 @@
         <v>73</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>63.46</v>
+        <v>62.99</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>66.68000000000001</v>
+        <v>68.20999999999999</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>64.05</v>
+        <v>68.17</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>64.05</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>64.8</v>
+        <v>68</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>69.83</v>
+        <v>69.12</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>67.43000000000001</v>
+        <v>68.09999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -2405,25 +2405,25 @@
         <v>75</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>75.15000000000001</v>
+        <v>73.47</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>67.11</v>
+        <v>67.88</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>66.53</v>
+        <v>68.31999999999999</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>68.39</v>
+        <v>68.45999999999999</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>73.43000000000001</v>
+        <v>69.55</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>75.14</v>
+        <v>70.28</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>70.75</v>
+        <v>71.72</v>
       </c>
     </row>
     <row r="15">
@@ -2436,25 +2436,25 @@
         <v>60</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>48.25</v>
+        <v>54.28</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>54.18</v>
+        <v>57.44</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>61.18</v>
+        <v>57.97</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>57</v>
+        <v>57.77</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>55.5</v>
+        <v>56.92</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>54.15</v>
+        <v>56.15</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>47.88</v>
+        <v>55.04</v>
       </c>
     </row>
     <row r="16">
@@ -2467,25 +2467,25 @@
         <v>52</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>51.14</v>
+        <v>50.26</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>46.7</v>
+        <v>60.42</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>59.56</v>
+        <v>60.68</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>58.82</v>
+        <v>60.58</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>56.37</v>
+        <v>57.13</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>54.85</v>
+        <v>57.16</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>37.22</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="17">
@@ -2498,25 +2498,25 @@
         <v>58</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>54.54</v>
+        <v>56.92</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>62.3</v>
+        <v>62.81</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>64.69</v>
+        <v>63.16</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>65.12</v>
+        <v>63.1</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>64.03</v>
+        <v>62.52</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>63.75</v>
+        <v>62.16</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>56.56</v>
+        <v>61.54</v>
       </c>
     </row>
     <row r="18">
@@ -2529,25 +2529,25 @@
         <v>71</v>
       </c>
       <c r="C18" s="3" t="n">
+        <v>68.25</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>69.93000000000001</v>
+      </c>
+      <c r="E18" s="3" t="n">
         <v>70.29000000000001</v>
       </c>
-      <c r="D18" s="3" t="n">
-        <v>69.48</v>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>71.5</v>
-      </c>
       <c r="F18" s="3" t="n">
-        <v>70.94</v>
+        <v>70.23999999999999</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>70.14</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>68.5</v>
+        <v>69.44</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>62.24</v>
+        <v>65.95999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -2560,25 +2560,25 @@
         <v>76</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>66.42</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>73.12</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>75.22</v>
+        <v>73.93000000000001</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>74.92</v>
+        <v>74.02</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>73.95999999999999</v>
+        <v>74</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>75.15000000000001</v>
+        <v>74.64</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>74.13</v>
+        <v>74.40000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -2591,25 +2591,25 @@
         <v>68</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>60.55</v>
+        <v>61.03</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>67.88</v>
+        <v>69.78</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>72.37</v>
+        <v>69.94</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>70.62</v>
+        <v>69.86</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>68.95</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>71.78</v>
+        <v>70.56999999999999</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>68.61</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21">
@@ -2622,25 +2622,25 @@
         <v>69</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>69.95999999999999</v>
+        <v>68.22</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>74.73999999999999</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>71.62</v>
+        <v>74.81</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>72.43000000000001</v>
+        <v>74.67</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>73.8</v>
+        <v>74.44</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>73.54000000000001</v>
+        <v>74.78</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>71.28</v>
+        <v>72.90000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -2653,25 +2653,25 @@
         <v>61</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>79.5</v>
+        <v>76.37</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>69.19</v>
+        <v>69.04000000000001</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>73.05</v>
+        <v>68.78</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>73.09999999999999</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>71.81</v>
+        <v>69.42</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>70.87</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>65.33</v>
+        <v>66.73</v>
       </c>
     </row>
     <row r="23">
@@ -2684,25 +2684,25 @@
         <v>43</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>55.39</v>
+        <v>59.25</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>43.01</v>
+        <v>48.06</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>45.86</v>
+        <v>48.56</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>47.2</v>
+        <v>48.66</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>46.08</v>
+        <v>48.71</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>41.5</v>
+        <v>47.87</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>39.68</v>
+        <v>48.26</v>
       </c>
     </row>
     <row r="24">
@@ -2715,25 +2715,25 @@
         <v>59</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>74.8</v>
+        <v>73.47</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>62.48</v>
+        <v>62.89</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>62.08</v>
+        <v>62.74</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>55.25</v>
+        <v>62.44</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>55.81</v>
+        <v>63.56</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>56.77</v>
+        <v>64.06999999999999</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>58.97</v>
+        <v>62.13</v>
       </c>
     </row>
     <row r="25">
@@ -2746,25 +2746,25 @@
         <v>53</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>48.83</v>
+        <v>44.62</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>48.34</v>
+        <v>56.89</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>59.36</v>
+        <v>55.46</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>60.47</v>
+        <v>55.34</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>57.52</v>
+        <v>53.3</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>59.43</v>
+        <v>53.38</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>51.08</v>
+        <v>50.25</v>
       </c>
     </row>
     <row r="26">
@@ -2777,25 +2777,25 @@
         <v>71</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>72.7</v>
+        <v>70.84</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>67.3</v>
+        <v>66.8</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>65.7</v>
+        <v>67.41</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>64.77</v>
+        <v>67.34999999999999</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>65.42</v>
+        <v>67.68000000000001</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>70.56</v>
+        <v>68.12</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>69.56</v>
+        <v>70.39</v>
       </c>
     </row>
     <row r="27">
@@ -2808,25 +2808,25 @@
         <v>43</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>51.98</v>
+        <v>46.17</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>48.22</v>
+        <v>57.94</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>55.12</v>
+        <v>57.89</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>55.76</v>
+        <v>55.65</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>55.29</v>
+        <v>52.5</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>54.78</v>
+        <v>52.62</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>37.21</v>
+        <v>46.88</v>
       </c>
     </row>
     <row r="28">
@@ -2839,25 +2839,25 @@
         <v>61</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>77.3</v>
+        <v>74.56999999999999</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>63.91</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>65.51000000000001</v>
+        <v>64.02</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>65.67</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>64.64</v>
+        <v>64.38</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>63.81</v>
+        <v>64.59</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>65.58</v>
+        <v>66.62</v>
       </c>
     </row>
     <row r="29">
@@ -2870,25 +2870,25 @@
         <v>66</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>71.12</v>
+        <v>66.54000000000001</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>65.26000000000001</v>
+        <v>69.55</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>73.04000000000001</v>
+        <v>70.08</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>70.02</v>
+        <v>70.05</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>71.86</v>
+        <v>69.5</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>69.94</v>
+        <v>68.69</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>61.32</v>
+        <v>67.53</v>
       </c>
     </row>
     <row r="30">
@@ -2901,25 +2901,25 @@
         <v>63</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>68.95</v>
+        <v>66.94</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>70.42</v>
+        <v>69.68000000000001</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>71.64</v>
+        <v>69.56</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>68.98</v>
+        <v>69.52</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>70.84999999999999</v>
+        <v>70.29000000000001</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>69.84</v>
+        <v>69.48</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>55.99</v>
+        <v>61.99</v>
       </c>
     </row>
     <row r="31">
@@ -2932,25 +2932,25 @@
         <v>50</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>54.79</v>
+        <v>57.65</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>53.66</v>
+        <v>57.18</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>58.91</v>
+        <v>55.72</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>57.2</v>
+        <v>55.57</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>54.47</v>
+        <v>54.78</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>50.81</v>
+        <v>54.75</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>47.16</v>
+        <v>51.58</v>
       </c>
     </row>
     <row r="32">
@@ -2963,25 +2963,25 @@
         <v>79</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>73.02</v>
+        <v>70</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>73.55</v>
+        <v>73.26000000000001</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>75.72</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>76.5</v>
+        <v>73.95</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>76.43000000000001</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>76.5</v>
+        <v>75.73</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>75.94</v>
+        <v>76.23999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -2994,25 +2994,25 @@
         <v>67</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>52.36</v>
+        <v>44.26</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>47.79</v>
+        <v>62.85</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>66.22</v>
+        <v>63.06</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>63.81</v>
+        <v>62.88</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>64.26000000000001</v>
+        <v>62.53</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>65.06999999999999</v>
+        <v>62.72</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>62.27</v>
+        <v>64.70999999999999</v>
       </c>
     </row>
     <row r="34">
@@ -3025,25 +3025,25 @@
         <v>66</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>57.53</v>
+        <v>60.77</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>64.26000000000001</v>
+        <v>65.77</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>61.25</v>
+        <v>64.17</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>62.47</v>
+        <v>64.15000000000001</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>61.99</v>
+        <v>64.31</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>61.3</v>
+        <v>63.5</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>59.58</v>
+        <v>62.34</v>
       </c>
     </row>
     <row r="35">
@@ -3056,25 +3056,25 @@
         <v>63</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>62.12</v>
+        <v>62.6</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>64.8</v>
+        <v>64.56</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>62.35</v>
+        <v>63.02</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>65.17</v>
+        <v>62.96</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>60.82</v>
+        <v>60.65</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>65.65000000000001</v>
+        <v>61.37</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>62.78</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="36">
@@ -3087,25 +3087,25 @@
         <v>77</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>80.37</v>
+        <v>76.08</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>77.01000000000001</v>
+        <v>74.66</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>76.44</v>
+        <v>75.06999999999999</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>76.34999999999999</v>
+        <v>75.17</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>76.45</v>
+        <v>75.7</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>76.76000000000001</v>
+        <v>75.95999999999999</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>78.98999999999999</v>
+        <v>77.54000000000001</v>
       </c>
     </row>
     <row r="37">
@@ -3118,25 +3118,25 @@
         <v>64</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>61.72</v>
+        <v>62.77</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>58.72</v>
+        <v>60.68</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>63.36</v>
+        <v>61.21</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>64.27</v>
+        <v>61.25</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>59.36</v>
+        <v>60.52</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>57.28</v>
+        <v>59.65</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>54.06</v>
+        <v>60.12</v>
       </c>
     </row>
     <row r="38">
@@ -3149,25 +3149,25 @@
         <v>64</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>63.25</v>
+        <v>63.98</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>67.05</v>
+        <v>68.33</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>70.81999999999999</v>
+        <v>68.63</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>69.75</v>
+        <v>68.61</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>64.56999999999999</v>
+        <v>67.42</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>63.27</v>
+        <v>67.37</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>64.37</v>
+        <v>67.12</v>
       </c>
     </row>
     <row r="39">
@@ -3180,25 +3180,25 @@
         <v>70</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>56.37</v>
+        <v>57.09</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>63.59</v>
+        <v>71.22</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>76.39</v>
+        <v>71.64</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>63.37</v>
+        <v>71.31999999999999</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>59.63</v>
+        <v>68.34999999999999</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>58.93</v>
+        <v>68.34999999999999</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>57.79</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="40">
@@ -3211,25 +3211,25 @@
         <v>82</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>71.12</v>
+        <v>70.36</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>76.77</v>
+        <v>77.04000000000001</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>68.73</v>
+        <v>77.31</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>70.61</v>
+        <v>77.38</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>80.43000000000001</v>
+        <v>78.16</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>77.09</v>
+        <v>78.45999999999999</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>80.70999999999999</v>
+        <v>80.73999999999999</v>
       </c>
     </row>
     <row r="41">
@@ -3242,25 +3242,25 @@
         <v>63</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>55.25</v>
+        <v>57.77</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>63.4</v>
+        <v>65.12</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>63.45</v>
+        <v>65.25</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>62.81</v>
+        <v>65.09</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>64.13</v>
+        <v>65.20999999999999</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>65.72</v>
+        <v>65.83</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>64.52</v>
+        <v>65.45999999999999</v>
       </c>
     </row>
     <row r="42">
@@ -3273,25 +3273,25 @@
         <v>81</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>75.09999999999999</v>
+        <v>72.72</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>77.42</v>
+        <v>76.44</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>76.18000000000001</v>
+        <v>76.89</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>74.13</v>
+        <v>76.78</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>77.18000000000001</v>
+        <v>78.02</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>78.84</v>
+        <v>78.81</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>77.81</v>
+        <v>78.18000000000001</v>
       </c>
     </row>
     <row r="43">
@@ -3304,25 +3304,25 @@
         <v>61</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>65.3</v>
+        <v>64.76000000000001</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>58.59</v>
+        <v>60.52</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>57.37</v>
+        <v>60.68</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>58.08</v>
+        <v>60.65</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>59.3</v>
+        <v>61.39</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>59.31</v>
+        <v>62.07</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>57.83</v>
+        <v>60.36</v>
       </c>
     </row>
     <row r="44">
@@ -3335,25 +3335,25 @@
         <v>48</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>54.06</v>
+        <v>57.33</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>48.75</v>
+        <v>52.34</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>55.58</v>
+        <v>52.96</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>50.52</v>
+        <v>52.97</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>53.45</v>
+        <v>52.86</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>49.23</v>
+        <v>53.37</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>50.74</v>
+        <v>54.32</v>
       </c>
     </row>
     <row r="45">
@@ -3366,25 +3366,25 @@
         <v>77</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>82.31</v>
+        <v>77.06</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>80.53</v>
+        <v>76.68000000000001</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>77.93000000000001</v>
+        <v>77.34999999999999</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>77.62</v>
+        <v>77.43000000000001</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>76.40000000000001</v>
+        <v>76.23</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>78.53</v>
+        <v>77.34999999999999</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>79.5</v>
+        <v>77.22</v>
       </c>
     </row>
   </sheetData>
